--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-06).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-06).xlsx
@@ -912,30 +912,30 @@
   </si>
   <si>
     <t>214
-178</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>R$ 1.845.806,88</t>
-  </si>
-  <si>
-    <t>R$ 9.663,91
-R$ 9.833,53</t>
-  </si>
-  <si>
-    <t>1.5%
+182</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>R$ 1.876.874,78</t>
+  </si>
+  <si>
+    <t>R$ 9.625,00
+R$ 9.788,11</t>
+  </si>
+  <si>
+    <t>1.6%
 3.3%</t>
   </si>
   <si>
-    <t>102.5</t>
-  </si>
-  <si>
-    <t>(6.0%)</t>
-  </si>
-  <si>
-    <t>24.3%</t>
+    <t>102.1</t>
+  </si>
+  <si>
+    <t>(5.9%)</t>
+  </si>
+  <si>
+    <t>24.1%</t>
   </si>
   <si>
     <t>(16.6%)</t>
@@ -947,34 +947,34 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>32.0</t>
-  </si>
-  <si>
-    <t>55.5%</t>
-  </si>
-  <si>
-    <t>20.7%</t>
-  </si>
-  <si>
-    <t>7.8</t>
+    <t>32.1</t>
+  </si>
+  <si>
+    <t>55.6%</t>
+  </si>
+  <si>
+    <t>21.0%</t>
+  </si>
+  <si>
+    <t>7.9</t>
   </si>
   <si>
     <t>8.7</t>
   </si>
   <si>
-    <t>16.9</t>
-  </si>
-  <si>
-    <t>23.3</t>
-  </si>
-  <si>
-    <t>56.5%</t>
+    <t>16.8</t>
+  </si>
+  <si>
+    <t>23.4</t>
+  </si>
+  <si>
+    <t>56.1%</t>
   </si>
   <si>
     <t>-R$ 56.833,28</t>
   </si>
   <si>
-    <t>2.97</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -4396,7 +4396,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4432,25 +4432,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>12290.639999999999</v>
+      </c>
+      <c r="P24" s="5">
+        <v>12290.639999999999</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.27145954713983045</v>
+      </c>
+      <c r="R24" s="7">
+        <v>145</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0.066176470588235281</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.35040567456210581</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.013147199820351098</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0018723597794744618</v>
+      </c>
+      <c r="X24" s="8">
+        <v>33.634064035087718</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.40350877192982454</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>7.3421298611111103</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>9.1071640350877185</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>23.643421052631577</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.32456140350877194</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>0</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5932,7 +5966,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5968,25 +6002,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>6546.5699999999997</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6546.5699999999997</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.17544914910349729</v>
+      </c>
+      <c r="R36" s="7">
+        <v>73</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.23728813559322037</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.3282637014497668</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.008980473744266082</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.065134108395694237</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.032987503379632389</v>
+      </c>
+      <c r="X36" s="8">
+        <v>33.651461403508769</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>12.027083333333334</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>5.3654767857142858</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>18.596177000000001</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>25.384794736842103</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.50877192982456143</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7849,7 +7919,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7885,25 +7955,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1439.7</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1439.7</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.14930452971554853</v>
+      </c>
+      <c r="R51" s="7">
+        <v>11</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.47619047619047616</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.2696395082308814</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.015470931444050843</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.07344342571369035</v>
+      </c>
+      <c r="X51" s="8">
+        <v>32.943750000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>1.9318181818181819</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>20.162500000000001</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>22.274999999999999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>29.175000000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.375</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12606,7 +12712,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12645,7 +12751,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12679,25 +12785,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>10790.99</v>
+      </c>
+      <c r="P89" s="5">
+        <v>10790.99</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.17174219060616158</v>
+      </c>
+      <c r="R89" s="7">
+        <v>94</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.24193548387096775</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.183698594846256</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.13602554538554851</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.020343128851013671</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0095887865710189701</v>
+      </c>
+      <c r="X89" s="8">
+        <v>60.116665789473686</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>22.077239784946237</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>20.142647058823531</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>47.693421052631578</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.078947368421052627</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -15457,7 +15597,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15810,7 +15950,7 @@
         <v>-383.10000000000002</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16721,7 +16861,7 @@
         <v>-366.30000000000001</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -16983,7 +17123,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17376,7 +17516,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18553,7 +18693,7 @@
         <v>-59.899999999999999</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18684,7 +18824,7 @@
         <v>-806.10000000000002</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20871,7 +21011,7 @@
         <v>-2523.1999999999998</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -20998,7 +21138,7 @@
         <v>264.19999999999999</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22153,7 +22293,7 @@
         <v>-1820.3599999999999</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24231,7 +24371,9 @@
       <c r="AB179" s="8">
         <v>2.8812859649122808</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>9.3888879999999997</v>
+      </c>
       <c r="AD179" s="8">
         <v>16.348538596491228</v>
       </c>
@@ -28312,7 +28454,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
